--- a/LISTEN/Script/22_12_n3/22_12.xlsx
+++ b/LISTEN/Script/22_12_n3/22_12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\LISTEN\Script\22_12_n3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C59B594A-F966-4F16-A255-D028CC11131A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82375A32-86EE-4EB8-A824-1CFFED68F660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14655" yWindow="15" windowWidth="20880" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14655" yWindow="15" windowWidth="20880" windowHeight="19995" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1番" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="153">
   <si>
     <t>Fre</t>
   </si>
@@ -39,355 +39,448 @@
     <t>History</t>
   </si>
   <si>
+    <t>招待客</t>
+  </si>
+  <si>
+    <t>しょうたいきゃく</t>
+  </si>
+  <si>
+    <t>来宾</t>
+  </si>
+  <si>
+    <t>文学</t>
+  </si>
+  <si>
+    <t>ぶんがく</t>
+  </si>
+  <si>
+    <t>世紀</t>
+  </si>
+  <si>
+    <t>せいき</t>
+  </si>
+  <si>
+    <t>倉庫</t>
+  </si>
+  <si>
+    <t>そうこ</t>
+  </si>
+  <si>
+    <t>奨学金</t>
+  </si>
+  <si>
+    <t>しょうがくきん</t>
+  </si>
+  <si>
+    <t>片付け</t>
+  </si>
+  <si>
+    <t>かたづけ</t>
+  </si>
+  <si>
+    <t>申請</t>
+  </si>
+  <si>
+    <t>しんせい</t>
+  </si>
+  <si>
+    <t>はっきり</t>
+  </si>
+  <si>
+    <t>清楚；明确；清晰</t>
+  </si>
+  <si>
+    <t>組み立てる</t>
+  </si>
+  <si>
+    <t>くみたてる</t>
+  </si>
+  <si>
+    <t>装配；组装；构建</t>
+  </si>
+  <si>
+    <t>書類</t>
+  </si>
+  <si>
+    <t>しょるい</t>
+  </si>
+  <si>
+    <t>文件；档案；资料</t>
+  </si>
+  <si>
+    <t>たぶん</t>
+  </si>
+  <si>
+    <t>大概；或许</t>
+  </si>
+  <si>
+    <t>混む</t>
+  </si>
+  <si>
+    <t>こむ</t>
+  </si>
+  <si>
+    <t>図</t>
+  </si>
+  <si>
+    <t>ず</t>
+  </si>
+  <si>
+    <t>图表；地图</t>
+  </si>
+  <si>
+    <t>代表者</t>
+  </si>
+  <si>
+    <t>だいひょうしゃ</t>
+  </si>
+  <si>
+    <t>申込書</t>
+  </si>
+  <si>
+    <t>もうしこみしょ</t>
+  </si>
+  <si>
+    <t>いつもの</t>
+  </si>
+  <si>
+    <t>平常的；往常的；惯常的</t>
+  </si>
+  <si>
+    <t>印刷</t>
+  </si>
+  <si>
+    <t>いんさつ</t>
+  </si>
+  <si>
+    <t>売り場</t>
+  </si>
+  <si>
+    <t>うりば</t>
+  </si>
+  <si>
+    <t>場合</t>
+  </si>
+  <si>
+    <t>ばあい</t>
+  </si>
+  <si>
+    <t>使用料</t>
+  </si>
+  <si>
+    <t>しようりょう</t>
+  </si>
+  <si>
+    <t>租金</t>
+  </si>
+  <si>
     <t>当日</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>とうじつ</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>図</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ず</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>图表；地图</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>壁</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>かべ</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>片付け</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>かたづけ</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>花瓶</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>かびん</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>倉庫</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>そうこ</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>位置</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>いち</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>何日</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>なんにち</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>はっきり</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>清楚；明确；清晰</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>読む</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>よむ</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>借り</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>かり</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>全体</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>ぜんたい</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>全部</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>場合</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ばあい</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>文学</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ぶんがく</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>世紀</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>せいき</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>説明</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>せつめい</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用料</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>しようりょう</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>租金</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>用紙</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>ようし</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>纸张；表格</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>利用</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>りよう</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>代表者</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>だいひょうしゃ</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>申込書</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>もうしこみしょ</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>借りる</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>かりる</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>来月</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>らいげつ</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>また今度</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>改天；下次再说</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>リボン</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>丝带；缎带</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>組み立てる</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>装配；组装；构建</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>くみたてる</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>詰める</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>つめる</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>塞满；填满；装入</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>箱</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>はこ</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>招待客</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>しょうたいきゃく</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>来宾</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>いつもの</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>平常的；往常的；惯常的</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>答える</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>こたえる</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>印刷</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>いんさつ</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>申請</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>しんせい</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>奨学金</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>しょうがくきん</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>書類</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>しょるい</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>文件；档案；资料</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>割引券</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>わりびきけん</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>混む</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>こむ</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>たぶん</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>大概；或许</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>売り場</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>うりば</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>遊園地</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>ゆうえんち</t>
+  </si>
+  <si>
+    <t>びっくり</t>
+  </si>
+  <si>
+    <t>吃惊；惊讶</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>売る</t>
+  </si>
+  <si>
+    <t>うる</t>
+  </si>
+  <si>
+    <t>活動</t>
+  </si>
+  <si>
+    <t>かつどう</t>
+  </si>
+  <si>
+    <t>00</t>
+  </si>
+  <si>
+    <t>相変わらず</t>
+  </si>
+  <si>
+    <t>あいかわらず</t>
+  </si>
+  <si>
+    <t>照旧；依然</t>
+  </si>
+  <si>
+    <t>泳ぐ</t>
+  </si>
+  <si>
+    <t>およぐ</t>
+  </si>
+  <si>
+    <t>幼稚園</t>
+  </si>
+  <si>
+    <t>ようちえん</t>
+  </si>
+  <si>
+    <t>係員</t>
+  </si>
+  <si>
+    <t>かかりいん</t>
+  </si>
+  <si>
+    <t>応答</t>
+  </si>
+  <si>
+    <t>おうとう</t>
+  </si>
+  <si>
+    <t>状態</t>
+  </si>
+  <si>
+    <t>じょうたい</t>
+  </si>
+  <si>
+    <t>波</t>
+  </si>
+  <si>
+    <t>なみ</t>
+  </si>
+  <si>
+    <t>南大島</t>
+  </si>
+  <si>
+    <t>みなみおおしま</t>
+  </si>
+  <si>
+    <t>船</t>
+  </si>
+  <si>
+    <t>ふね</t>
+  </si>
+  <si>
+    <t>肘</t>
+  </si>
+  <si>
+    <t>ひじ</t>
+  </si>
+  <si>
+    <t>効果</t>
+  </si>
+  <si>
+    <t>こうか</t>
+  </si>
+  <si>
+    <t>短い</t>
+  </si>
+  <si>
+    <t>みじかい</t>
+  </si>
+  <si>
+    <t>遊ぶ</t>
+  </si>
+  <si>
+    <t>あそぶ</t>
+  </si>
+  <si>
+    <t>めずらしい</t>
+  </si>
+  <si>
+    <t>小型</t>
+  </si>
+  <si>
+    <t>こがた</t>
+  </si>
+  <si>
+    <t>先月</t>
+  </si>
+  <si>
+    <t>せんげつ</t>
+  </si>
+  <si>
+    <t>前回</t>
+  </si>
+  <si>
+    <t>ぜんかい</t>
+  </si>
+  <si>
+    <t>街</t>
+  </si>
+  <si>
+    <t>まち</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>必ず</t>
+  </si>
+  <si>
+    <t>かならず</t>
+  </si>
+  <si>
+    <t>体力</t>
+  </si>
+  <si>
+    <t>たいりょく</t>
+  </si>
+  <si>
+    <t>中止</t>
+  </si>
+  <si>
+    <t>ちゅうし</t>
+  </si>
+  <si>
+    <t>出発</t>
+  </si>
+  <si>
+    <t>しゅっぱつ</t>
+  </si>
+  <si>
+    <t>肩</t>
+  </si>
+  <si>
+    <t>かた</t>
+  </si>
+  <si>
+    <t>内容</t>
+  </si>
+  <si>
+    <t>ないよう</t>
+  </si>
+  <si>
+    <t>基本</t>
+  </si>
+  <si>
+    <t>きほん</t>
+  </si>
+  <si>
+    <t>珍しい</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -452,13 +545,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -762,18 +852,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="9" style="2" customWidth="1"/>
-    <col min="2" max="2" width="14.75" style="2" customWidth="1"/>
-    <col min="3" max="3" width="19.5" style="2" customWidth="1"/>
-    <col min="4" max="4" width="25" style="2" customWidth="1"/>
-    <col min="5" max="5" width="9" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="2" max="2" width="14.75" customWidth="1"/>
+    <col min="3" max="3" width="19.5" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="5" max="5" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -786,491 +875,613 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A2" s="2">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A2">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A3" s="2">
-        <v>0</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="D2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A3">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="C3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A4" s="2">
-        <v>0</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="E3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A5" s="2">
-        <v>0</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="E4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A6" s="2">
-        <v>0</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A7" s="2">
-        <v>0</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="E6">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A8" s="2">
-        <v>0</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="E7">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A9" s="2">
-        <v>0</v>
-      </c>
-      <c r="B9" s="2" t="s">
+      <c r="E8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A9">
+        <v>2</v>
+      </c>
+      <c r="B9" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A10" s="2">
-        <v>0</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="E9">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="C10" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A11" s="2">
-        <v>0</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="D10" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="E10">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A12" s="2">
-        <v>0</v>
-      </c>
-      <c r="B12" s="2" t="s">
+      <c r="C11" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D11" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A13" s="2">
-        <v>0</v>
-      </c>
-      <c r="B13" s="2" t="s">
+      <c r="E11">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C12" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E12">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A14" s="2">
-        <v>0</v>
-      </c>
-      <c r="B14" s="2" t="s">
+      <c r="C13" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="E13">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A15" s="2">
-        <v>0</v>
-      </c>
-      <c r="B15" s="2" t="s">
+      <c r="C14" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D14" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A16" s="2">
-        <v>0</v>
-      </c>
-      <c r="B16" s="2" t="s">
+      <c r="E14">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C15" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A17" s="2">
-        <v>0</v>
-      </c>
-      <c r="B17" s="2" t="s">
+      <c r="E15">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C16" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A18" s="2">
-        <v>0</v>
-      </c>
-      <c r="B18" s="2" t="s">
+      <c r="E16">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D17" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="E17">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A19" s="2">
-        <v>0</v>
-      </c>
-      <c r="B19" s="2" t="s">
+      <c r="C18" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="E18">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A19">
+        <v>1</v>
+      </c>
+      <c r="B19" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="C19" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A20" s="2">
-        <v>0</v>
-      </c>
-      <c r="B20" s="2" t="s">
+      <c r="E19">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A20">
+        <v>1</v>
+      </c>
+      <c r="B20" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A21" s="2">
-        <v>0</v>
-      </c>
-      <c r="B21" s="2" t="s">
+      <c r="E20">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A21">
+        <v>1</v>
+      </c>
+      <c r="B21" t="s">
         <v>47</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A22" s="2">
-        <v>0</v>
-      </c>
-      <c r="B22" s="2" t="s">
+      <c r="D21" t="s">
         <v>49</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="E21">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A22">
+        <v>0</v>
+      </c>
+      <c r="B22" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A23" s="2">
-        <v>0</v>
-      </c>
-      <c r="B23" s="2" t="s">
+      <c r="C22" t="s">
         <v>51</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="E22">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A23">
+        <v>0</v>
+      </c>
+      <c r="B23" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A24" s="2">
-        <v>0</v>
-      </c>
-      <c r="B24" s="2" t="s">
+      <c r="C23" t="s">
         <v>53</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="E23">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A24">
+        <v>0</v>
+      </c>
+      <c r="B24" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A25" s="2">
-        <v>0</v>
-      </c>
-      <c r="B25" s="2" t="s">
+      <c r="C24" t="s">
         <v>55</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="E24">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A25">
+        <v>0</v>
+      </c>
+      <c r="B25" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A26" s="2">
-        <v>0</v>
-      </c>
-      <c r="B26" s="2" t="s">
+      <c r="C25" t="s">
         <v>57</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="E25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A26">
+        <v>0</v>
+      </c>
+      <c r="B26" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A27" s="2">
-        <v>0</v>
-      </c>
-      <c r="B27" s="2" t="s">
+      <c r="C26" t="s">
         <v>59</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="E26">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A27">
+        <v>0</v>
+      </c>
+      <c r="B27" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" t="s">
         <v>61</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A28" s="2">
-        <v>0</v>
-      </c>
-      <c r="B28" s="2" t="s">
+      <c r="E27">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A28">
+        <v>0</v>
+      </c>
+      <c r="B28" t="s">
         <v>62</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" t="s">
         <v>63</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="E28">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A29">
+        <v>0</v>
+      </c>
+      <c r="B29" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A29" s="2">
-        <v>0</v>
-      </c>
-      <c r="B29" s="2" t="s">
+      <c r="C29" t="s">
         <v>65</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A30" s="2">
-        <v>0</v>
-      </c>
-      <c r="B30" s="2" t="s">
+      <c r="E29">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" t="s">
         <v>68</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="E30">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A31">
+        <v>0</v>
+      </c>
+      <c r="B31" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A31" s="2">
-        <v>0</v>
-      </c>
-      <c r="B31" s="2" t="s">
+      <c r="C31" t="s">
         <v>70</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A32" s="2">
-        <v>0</v>
-      </c>
-      <c r="B32" s="2" t="s">
+      <c r="E31">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A32">
+        <v>0</v>
+      </c>
+      <c r="B32" t="s">
         <v>72</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A33" s="2">
-        <v>0</v>
-      </c>
-      <c r="B33" s="2" t="s">
+      <c r="E32">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A33">
+        <v>0</v>
+      </c>
+      <c r="B33" t="s">
         <v>74</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A34" s="2">
-        <v>0</v>
-      </c>
-      <c r="B34" s="2" t="s">
+      <c r="E33">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A34">
+        <v>0</v>
+      </c>
+      <c r="B34" t="s">
         <v>76</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A35" s="2">
-        <v>0</v>
-      </c>
-      <c r="B35" s="2" t="s">
+      <c r="E34">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A35">
+        <v>0</v>
+      </c>
+      <c r="B35" t="s">
         <v>78</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="D35" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A36" s="2">
-        <v>0</v>
-      </c>
-      <c r="B36" s="2" t="s">
+      <c r="E35">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A36">
+        <v>0</v>
+      </c>
+      <c r="B36" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="D36" t="s">
         <v>81</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="E36">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A37">
+        <v>0</v>
+      </c>
+      <c r="B37" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A37" s="2">
-        <v>0</v>
-      </c>
-      <c r="B37" s="2" t="s">
+      <c r="C37" t="s">
         <v>83</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="D37" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A38" s="2">
-        <v>0</v>
-      </c>
-      <c r="B38" s="2" t="s">
+      <c r="E37">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A38">
+        <v>0</v>
+      </c>
+      <c r="B38" t="s">
         <v>85</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A39" s="2">
-        <v>0</v>
-      </c>
-      <c r="B39" s="2" t="s">
+      <c r="E38">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A39">
+        <v>0</v>
+      </c>
+      <c r="B39" t="s">
         <v>87</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A40" s="2">
-        <v>0</v>
-      </c>
-      <c r="B40" s="2" t="s">
+      <c r="E39">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A40">
+        <v>0</v>
+      </c>
+      <c r="B40" t="s">
         <v>89</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A41" s="2">
-        <v>0</v>
-      </c>
-      <c r="B41" s="2" t="s">
+      <c r="E40">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A41">
+        <v>0</v>
+      </c>
+      <c r="B41" t="s">
         <v>91</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" t="s">
         <v>92</v>
+      </c>
+      <c r="E41">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="16.375" customWidth="1"/>
     <col min="3" max="3" width="23.5" customWidth="1"/>
     <col min="4" max="4" width="28.875" customWidth="1"/>
-    <col min="5" max="5" width="9" customWidth="1"/>
+    <col min="5" max="6" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1282,11 +1493,410 @@
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" t="s">
+        <v>107</v>
+      </c>
+      <c r="E7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>110</v>
+      </c>
+      <c r="C9" t="s">
+        <v>111</v>
+      </c>
+      <c r="E9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C10" t="s">
+        <v>113</v>
+      </c>
+      <c r="E10" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11" t="s">
+        <v>114</v>
+      </c>
+      <c r="C11" t="s">
+        <v>115</v>
+      </c>
+      <c r="E11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A12">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C12" t="s">
+        <v>117</v>
+      </c>
+      <c r="E12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C13" t="s">
+        <v>119</v>
+      </c>
+      <c r="E13" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A14">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C14" t="s">
+        <v>121</v>
+      </c>
+      <c r="E14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15" t="s">
+        <v>122</v>
+      </c>
+      <c r="C15" t="s">
+        <v>123</v>
+      </c>
+      <c r="E15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16" t="s">
+        <v>124</v>
+      </c>
+      <c r="C16" t="s">
+        <v>125</v>
+      </c>
+      <c r="E16" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17" t="s">
+        <v>126</v>
+      </c>
+      <c r="C17" t="s">
+        <v>127</v>
+      </c>
+      <c r="E17" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18" t="s">
+        <v>152</v>
+      </c>
+      <c r="C18" t="s">
+        <v>128</v>
+      </c>
+      <c r="E18" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>129</v>
+      </c>
+      <c r="C19" t="s">
+        <v>130</v>
+      </c>
+      <c r="E19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A20">
+        <v>1</v>
+      </c>
+      <c r="B20" t="s">
+        <v>131</v>
+      </c>
+      <c r="C20" t="s">
+        <v>132</v>
+      </c>
+      <c r="E20" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A21">
+        <v>1</v>
+      </c>
+      <c r="B21" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" t="s">
+        <v>134</v>
+      </c>
+      <c r="E21" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A22">
+        <v>0</v>
+      </c>
+      <c r="B22" t="s">
+        <v>135</v>
+      </c>
+      <c r="C22" t="s">
+        <v>136</v>
+      </c>
+      <c r="E22" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A23">
+        <v>0</v>
+      </c>
+      <c r="B23" t="s">
+        <v>138</v>
+      </c>
+      <c r="C23" t="s">
+        <v>139</v>
+      </c>
+      <c r="E23" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A24">
+        <v>0</v>
+      </c>
+      <c r="B24" t="s">
+        <v>140</v>
+      </c>
+      <c r="C24" t="s">
+        <v>141</v>
+      </c>
+      <c r="E24" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A25">
+        <v>0</v>
+      </c>
+      <c r="B25" t="s">
+        <v>142</v>
+      </c>
+      <c r="C25" t="s">
+        <v>143</v>
+      </c>
+      <c r="E25" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A26">
+        <v>0</v>
+      </c>
+      <c r="B26" t="s">
+        <v>144</v>
+      </c>
+      <c r="C26" t="s">
+        <v>145</v>
+      </c>
+      <c r="E26" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A27">
+        <v>0</v>
+      </c>
+      <c r="B27" t="s">
+        <v>146</v>
+      </c>
+      <c r="C27" t="s">
+        <v>147</v>
+      </c>
+      <c r="E27" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A28">
+        <v>0</v>
+      </c>
+      <c r="B28" t="s">
+        <v>148</v>
+      </c>
+      <c r="C28" t="s">
+        <v>149</v>
+      </c>
+      <c r="E28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A29">
+        <v>0</v>
+      </c>
+      <c r="B29" t="s">
+        <v>150</v>
+      </c>
+      <c r="C29" t="s">
+        <v>151</v>
+      </c>
+      <c r="E29" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1299,7 +1909,7 @@
     <col min="2" max="2" width="23.375" customWidth="1"/>
     <col min="3" max="3" width="17.625" customWidth="1"/>
     <col min="4" max="4" width="32.125" customWidth="1"/>
-    <col min="5" max="6" width="9" customWidth="1"/>
+    <col min="5" max="5" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.15">

--- a/LISTEN/Script/22_12_n3/22_12.xlsx
+++ b/LISTEN/Script/22_12_n3/22_12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\LISTEN\Script\22_12_n3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82375A32-86EE-4EB8-A824-1CFFED68F660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F828F51-69D5-4651-B463-620B8D9F6159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14655" yWindow="15" windowWidth="20880" windowHeight="19995" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14655" yWindow="15" windowWidth="20880" windowHeight="19995" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1番" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="210">
   <si>
     <t>Fre</t>
   </si>
@@ -481,6 +481,234 @@
   </si>
   <si>
     <t>珍しい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>情報</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>じょうほう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>方法</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ほうほう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>選ぶ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>えらぶ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>想像</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>そうぞう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>選択</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>せんたく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>興味</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>きょうみ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>目的</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>もくてき</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>申し込み</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>もうしこみ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>専門科目</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>せんもんかもく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>捨て方</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>すてかた</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>丢弃方法；处理方式</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>工夫</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>くふう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>设法，想办法</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>防ぐ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ふせぐ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>おやつ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>点心;零食</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>残す</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>のこす</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>結局</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>けっきょく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>コロッケ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>炸肉饼；炸土豆饼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>状態</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>じょうたい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>空く</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>すく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>空闲；稀疏；变少</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>お腹</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>おなか</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>効果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>こうか</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>早起き</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>はやおき</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>慣れる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>なれる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>最初</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>さいしょ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>集中</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>しゅうちゅう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>混む</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>こむ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>英語</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>えいご</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>出勤</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>しゅっきん</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -545,10 +773,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1902,14 +2133,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="11.25" customWidth="1"/>
-    <col min="2" max="2" width="23.375" customWidth="1"/>
-    <col min="3" max="3" width="17.625" customWidth="1"/>
-    <col min="4" max="4" width="32.125" customWidth="1"/>
-    <col min="5" max="5" width="9" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="2" customWidth="1"/>
+    <col min="2" max="2" width="23.375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="17.625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="32.125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="9" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.15">
@@ -1929,8 +2161,315 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A2" s="2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A3" s="2">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A4" s="2">
+        <v>0</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A5" s="2">
+        <v>0</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A6" s="2">
+        <v>0</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A7" s="2">
+        <v>0</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A8" s="2">
+        <v>0</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A9" s="2">
+        <v>0</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A10" s="2">
+        <v>0</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A11" s="2">
+        <v>0</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A12" s="2">
+        <v>0</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A13" s="2">
+        <v>0</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A14" s="2">
+        <v>0</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A15" s="2">
+        <v>0</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A16" s="2">
+        <v>0</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A17" s="2">
+        <v>0</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A18" s="2">
+        <v>0</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A19" s="2">
+        <v>0</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A20" s="2">
+        <v>0</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A21" s="2">
+        <v>0</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A22" s="2">
+        <v>0</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A23" s="2">
+        <v>0</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A24" s="2">
+        <v>0</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A25" s="2">
+        <v>0</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A26" s="2">
+        <v>0</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A27" s="2">
+        <v>0</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A28" s="2">
+        <v>0</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>